--- a/grupos/1CV - Estadisticos 20241.xlsx
+++ b/grupos/1CV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="89">
   <si>
     <t>Materia</t>
   </si>
@@ -200,21 +200,21 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Ramírez Vargas Miranda Alejandra</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
@@ -233,94 +233,58 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ANGUIANO</t>
+    <t>VASQUEZ</t>
   </si>
   <si>
     <t>BAUTISTA</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
     <t>MORA</t>
   </si>
   <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>URBANO</t>
-  </si>
-  <si>
-    <t>ZUNO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>CHAPARRO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ARELI CICLARI</t>
+    <t>DANIELA LILI</t>
   </si>
   <si>
     <t>LUZ ELENA</t>
   </si>
   <si>
+    <t>MAYKA XIMENA</t>
+  </si>
+  <si>
+    <t>EUNICE GUADALUPE</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>EUNICE GUADALUPE</t>
-  </si>
-  <si>
-    <t>EMIRETH</t>
-  </si>
-  <si>
     <t>BRENDA</t>
-  </si>
-  <si>
-    <t>DAFNE</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>PAOLA MELANIE</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
-    <t>ALIN MARIEL</t>
   </si>
 </sst>
 </file>
@@ -869,22 +833,22 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -917,22 +881,22 @@
         <v>6</v>
       </c>
       <c r="AA4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>10</v>
       </c>
       <c r="AD4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE4">
         <v>7</v>
       </c>
       <c r="AF4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -952,40 +916,40 @@
         <v>6</v>
       </c>
       <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>-1</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>10</v>
-      </c>
-      <c r="J5">
-        <v>-1</v>
-      </c>
-      <c r="K5">
-        <v>-1</v>
-      </c>
-      <c r="L5">
-        <v>-1</v>
-      </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1021,7 +985,7 @@
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -1071,22 +1035,22 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1119,22 +1083,22 @@
         <v>7</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE6">
         <v>9</v>
       </c>
       <c r="AF6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1172,22 +1136,22 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1220,10 +1184,10 @@
         <v>7</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>10</v>
@@ -1255,7 +1219,7 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -1273,22 +1237,22 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1327,7 +1291,7 @@
         <v>5</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD8">
         <v>5</v>
@@ -1356,7 +1320,7 @@
         <v>6</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -1374,22 +1338,22 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1422,10 +1386,10 @@
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC9">
         <v>5</v>
@@ -1475,22 +1439,22 @@
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1526,7 +1490,7 @@
         <v>9</v>
       </c>
       <c r="AB10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>10</v>
@@ -1535,10 +1499,10 @@
         <v>9</v>
       </c>
       <c r="AE10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1558,40 +1522,40 @@
         <v>4</v>
       </c>
       <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>6</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <v>-1</v>
+      </c>
+      <c r="K11">
+        <v>8</v>
+      </c>
+      <c r="L11">
         <v>4</v>
       </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-      <c r="G11">
-        <v>6</v>
-      </c>
-      <c r="H11">
-        <v>5</v>
-      </c>
-      <c r="I11">
-        <v>10</v>
-      </c>
-      <c r="J11">
-        <v>-1</v>
-      </c>
-      <c r="K11">
-        <v>-1</v>
-      </c>
-      <c r="L11">
-        <v>-1</v>
-      </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1624,22 +1588,22 @@
         <v>6</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB11">
         <v>5</v>
       </c>
       <c r="AC11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE11">
         <v>6</v>
       </c>
       <c r="AF11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1677,22 +1641,22 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1728,16 +1692,16 @@
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD12">
         <v>7</v>
       </c>
       <c r="AE12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF12">
         <v>9</v>
@@ -1778,22 +1742,22 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1826,13 +1790,13 @@
         <v>7</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD13">
         <v>10</v>
@@ -1841,7 +1805,7 @@
         <v>9</v>
       </c>
       <c r="AF13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1879,22 +1843,22 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1930,7 +1894,7 @@
         <v>6</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1939,10 +1903,10 @@
         <v>10</v>
       </c>
       <c r="AE14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -1980,22 +1944,22 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -2031,10 +1995,10 @@
         <v>7</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD15">
         <v>10</v>
@@ -2081,22 +2045,22 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -2129,10 +2093,10 @@
         <v>8</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>10</v>
@@ -2144,7 +2108,7 @@
         <v>8</v>
       </c>
       <c r="AF16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2182,22 +2146,22 @@
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2233,19 +2197,19 @@
         <v>5</v>
       </c>
       <c r="AB17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD17">
         <v>7</v>
       </c>
       <c r="AE17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2265,7 +2229,7 @@
         <v>4</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -2283,22 +2247,22 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2366,7 +2330,7 @@
         <v>4</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -2384,22 +2348,22 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2461,7 +2425,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -2485,22 +2449,22 @@
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2533,22 +2497,22 @@
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC20">
         <v>7</v>
       </c>
       <c r="AD20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE20">
         <v>7</v>
       </c>
       <c r="AF20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2562,7 +2526,7 @@
         <v>6</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -2586,22 +2550,22 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2634,16 +2598,16 @@
         <v>6</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE21">
         <v>8</v>
@@ -2669,7 +2633,7 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>8</v>
@@ -2687,22 +2651,22 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2738,19 +2702,19 @@
         <v>10</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE22">
         <v>7</v>
       </c>
       <c r="AF22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2788,22 +2752,22 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2836,22 +2800,22 @@
         <v>6</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE23">
         <v>8</v>
       </c>
       <c r="AF23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG23">
         <v>10</v>
@@ -2889,22 +2853,22 @@
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2937,16 +2901,16 @@
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE24">
         <v>8</v>
@@ -2990,22 +2954,22 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -3038,22 +3002,22 @@
         <v>8</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC25">
         <v>9</v>
       </c>
       <c r="AD25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE25">
         <v>8</v>
       </c>
       <c r="AF25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3091,22 +3055,22 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -3139,22 +3103,22 @@
         <v>8</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC26">
         <v>10</v>
       </c>
       <c r="AD26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE26">
         <v>10</v>
       </c>
       <c r="AF26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3192,22 +3156,22 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -3246,7 +3210,7 @@
         <v>6</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD27">
         <v>5</v>
@@ -3293,22 +3257,22 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -3347,16 +3311,16 @@
         <v>5</v>
       </c>
       <c r="AC28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD28">
         <v>5</v>
       </c>
       <c r="AE28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3394,22 +3358,22 @@
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -3442,22 +3406,22 @@
         <v>6</v>
       </c>
       <c r="AA29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD29">
         <v>8</v>
       </c>
       <c r="AE29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3495,22 +3459,22 @@
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -3546,7 +3510,7 @@
         <v>8</v>
       </c>
       <c r="AB30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC30">
         <v>8</v>
@@ -3555,10 +3519,10 @@
         <v>9</v>
       </c>
       <c r="AE30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3578,7 +3542,7 @@
         <v>6</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31">
         <v>6</v>
@@ -3596,22 +3560,22 @@
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3647,7 +3611,7 @@
         <v>10</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC31">
         <v>5</v>
@@ -3656,7 +3620,7 @@
         <v>6</v>
       </c>
       <c r="AE31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF31">
         <v>5</v>
@@ -3697,22 +3661,22 @@
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3748,19 +3712,19 @@
         <v>6</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>9</v>
       </c>
       <c r="AD32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3780,7 +3744,7 @@
         <v>8</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F33">
         <v>5</v>
@@ -3798,22 +3762,22 @@
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3849,13 +3813,13 @@
         <v>8</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC33">
         <v>5</v>
       </c>
       <c r="AD33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE33">
         <v>6</v>
@@ -3881,7 +3845,7 @@
         <v>4</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F34">
         <v>6</v>
@@ -3899,22 +3863,22 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3956,10 +3920,10 @@
         <v>5</v>
       </c>
       <c r="AD34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF34">
         <v>5</v>
@@ -4000,22 +3964,22 @@
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -4051,10 +4015,10 @@
         <v>8</v>
       </c>
       <c r="AB35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD35">
         <v>9</v>
@@ -4063,7 +4027,7 @@
         <v>10</v>
       </c>
       <c r="AF35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG35">
         <v>10</v>
@@ -4083,7 +4047,7 @@
         <v>7</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36">
         <v>9</v>
@@ -4101,22 +4065,22 @@
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -4149,16 +4113,16 @@
         <v>6</v>
       </c>
       <c r="AA36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB36">
         <v>7</v>
       </c>
       <c r="AC36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE36">
         <v>8</v>
@@ -4339,10 +4303,10 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M4">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -4351,7 +4315,7 @@
         <v>93.8</v>
       </c>
       <c r="P4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -4363,10 +4327,10 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U4">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -4375,7 +4339,7 @@
         <v>93.8</v>
       </c>
       <c r="X4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y4">
         <v>100</v>
@@ -4416,13 +4380,13 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N5">
-        <v>90</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -4440,13 +4404,13 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="V5">
-        <v>90</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -4493,13 +4457,13 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="M6">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="N6">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -4517,13 +4481,13 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="U6">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="V6">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="W6">
         <v>100</v>
@@ -4570,7 +4534,7 @@
         <v>100</v>
       </c>
       <c r="L7">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -4594,7 +4558,7 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -4647,16 +4611,16 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>90</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M8">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="N8">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O8">
-        <v>68.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -4671,16 +4635,16 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>90</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="U8">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="V8">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W8">
-        <v>68.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="X8">
         <v>100</v>
@@ -4724,16 +4688,16 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M9">
         <v>80</v>
       </c>
       <c r="N9">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="O9">
-        <v>68.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -4748,16 +4712,16 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="U9">
         <v>80</v>
       </c>
       <c r="V9">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="W9">
-        <v>68.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="X9">
         <v>100</v>
@@ -4878,13 +4842,13 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>95</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M11">
         <v>93.3</v>
       </c>
       <c r="N11">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O11">
         <v>87.5</v>
@@ -4902,13 +4866,13 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>95</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U11">
         <v>93.3</v>
       </c>
       <c r="V11">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W11">
         <v>87.5</v>
@@ -4958,7 +4922,7 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="N12">
         <v>100</v>
@@ -4982,7 +4946,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -5032,16 +4996,16 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M13">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -5056,16 +5020,16 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U13">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="V13">
         <v>100</v>
       </c>
       <c r="W13">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X13">
         <v>100</v>
@@ -5118,7 +5082,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -5142,7 +5106,7 @@
         <v>100</v>
       </c>
       <c r="W14">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X14">
         <v>100</v>
@@ -5186,16 +5150,16 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M15">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="N15">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O15">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -5210,16 +5174,16 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U15">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="V15">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W15">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="X15">
         <v>100</v>
@@ -5263,16 +5227,16 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M16">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="N16">
         <v>100</v>
       </c>
       <c r="O16">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -5287,16 +5251,16 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U16">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="V16">
         <v>100</v>
       </c>
       <c r="W16">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X16">
         <v>100</v>
@@ -5343,10 +5307,10 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N17">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -5367,10 +5331,10 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="V17">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W17">
         <v>100</v>
@@ -5417,19 +5381,19 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>68.2</v>
       </c>
       <c r="M18">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N18">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O18">
-        <v>93.8</v>
+        <v>53.1</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -5441,19 +5405,19 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>100</v>
+        <v>68.2</v>
       </c>
       <c r="U18">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="V18">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="W18">
-        <v>93.8</v>
+        <v>53.1</v>
       </c>
       <c r="X18">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Y18">
         <v>100</v>
@@ -5494,19 +5458,19 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O19">
         <v>93.8</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -5518,19 +5482,19 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="U19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="V19">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W19">
         <v>93.8</v>
       </c>
       <c r="X19">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Y19">
         <v>100</v>
@@ -5571,7 +5535,7 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M20">
         <v>80</v>
@@ -5580,7 +5544,7 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -5595,7 +5559,7 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U20">
         <v>80</v>
@@ -5604,7 +5568,7 @@
         <v>100</v>
       </c>
       <c r="W20">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X20">
         <v>100</v>
@@ -5648,10 +5612,10 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M21">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="N21">
         <v>100</v>
@@ -5672,10 +5636,10 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="U21">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -5725,16 +5689,16 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="M22">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="N22">
         <v>100</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -5749,16 +5713,16 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="U22">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="V22">
         <v>100</v>
       </c>
       <c r="W22">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X22">
         <v>100</v>
@@ -5802,10 +5766,10 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M23">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -5826,10 +5790,10 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U23">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -5882,13 +5846,13 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="N24">
         <v>100</v>
       </c>
       <c r="O24">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5906,13 +5870,13 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="V24">
         <v>100</v>
       </c>
       <c r="W24">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="X24">
         <v>100</v>
@@ -5956,10 +5920,10 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M25">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="N25">
         <v>100</v>
@@ -5980,10 +5944,10 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U25">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -6033,7 +5997,7 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -6057,7 +6021,7 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -6110,16 +6074,16 @@
         <v>100</v>
       </c>
       <c r="L27">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M27">
-        <v>80</v>
+        <v>76.7</v>
       </c>
       <c r="N27">
-        <v>90</v>
+        <v>85.7</v>
       </c>
       <c r="O27">
-        <v>81.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -6134,16 +6098,16 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U27">
-        <v>80</v>
+        <v>76.7</v>
       </c>
       <c r="V27">
-        <v>90</v>
+        <v>85.7</v>
       </c>
       <c r="W27">
-        <v>81.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="X27">
         <v>100</v>
@@ -6187,16 +6151,16 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M28">
         <v>80</v>
       </c>
       <c r="N28">
-        <v>95</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O28">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -6211,16 +6175,16 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U28">
         <v>80</v>
       </c>
       <c r="V28">
-        <v>95</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="W28">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="X28">
         <v>100</v>
@@ -6273,7 +6237,7 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -6297,7 +6261,7 @@
         <v>100</v>
       </c>
       <c r="W29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X29">
         <v>100</v>
@@ -6341,16 +6305,16 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N30">
         <v>100</v>
       </c>
       <c r="O30">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -6365,16 +6329,16 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U30">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="V30">
         <v>100</v>
       </c>
       <c r="W30">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X30">
         <v>100</v>
@@ -6418,16 +6382,16 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M31">
         <v>86.7</v>
       </c>
       <c r="N31">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O31">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -6442,16 +6406,16 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U31">
         <v>86.7</v>
       </c>
       <c r="V31">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W31">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X31">
         <v>100</v>
@@ -6495,16 +6459,16 @@
         <v>100</v>
       </c>
       <c r="L32">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M32">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N32">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O32">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P32">
         <v>100</v>
@@ -6519,16 +6483,16 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U32">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="V32">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W32">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X32">
         <v>100</v>
@@ -6572,16 +6536,16 @@
         <v>100</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M33">
         <v>86.7</v>
       </c>
       <c r="N33">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O33">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -6596,16 +6560,16 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U33">
         <v>86.7</v>
       </c>
       <c r="V33">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W33">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X33">
         <v>100</v>
@@ -6628,7 +6592,7 @@
         <v>95</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F34">
         <v>90</v>
@@ -6649,16 +6613,16 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>95</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N34">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O34">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -6673,16 +6637,16 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>95</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="V34">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W34">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X34">
         <v>100</v>
@@ -6726,7 +6690,7 @@
         <v>100</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M35">
         <v>93.3</v>
@@ -6735,7 +6699,7 @@
         <v>100</v>
       </c>
       <c r="O35">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P35">
         <v>100</v>
@@ -6750,7 +6714,7 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U35">
         <v>93.3</v>
@@ -6759,7 +6723,7 @@
         <v>100</v>
       </c>
       <c r="W35">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X35">
         <v>100</v>
@@ -6803,13 +6767,13 @@
         <v>100</v>
       </c>
       <c r="L36">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M36">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="N36">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O36">
         <v>93.8</v>
@@ -6827,13 +6791,13 @@
         <v>100</v>
       </c>
       <c r="T36">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U36">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="V36">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="W36">
         <v>93.8</v>
@@ -6908,19 +6872,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>45.5</v>
+        <v>69.7</v>
       </c>
       <c r="G2" s="2">
-        <v>54.5</v>
+        <v>30.3</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6931,7 +6895,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -6940,19 +6904,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>66.7</v>
+        <v>75.8</v>
       </c>
       <c r="G3" s="2">
-        <v>33.3</v>
+        <v>24.2</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6963,7 +6927,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -6972,19 +6936,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2">
-        <v>69.7</v>
+        <v>75.8</v>
       </c>
       <c r="G4" s="2">
-        <v>30.3</v>
+        <v>24.2</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6995,7 +6959,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -7004,19 +6968,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>69.7</v>
+        <v>78.8</v>
       </c>
       <c r="G5" s="2">
-        <v>30.3</v>
+        <v>21.2</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7027,7 +6991,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -7036,19 +7000,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>75.8</v>
+        <v>78.8</v>
       </c>
       <c r="G6" s="2">
-        <v>24.2</v>
+        <v>21.2</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7059,7 +7023,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
@@ -7080,7 +7044,7 @@
         <v>18.2</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7194,7 +7158,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7226,22 +7190,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920217</v>
+        <v>24330051920330</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7249,22 +7213,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920217</v>
+        <v>24330051920330</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7278,13 +7242,13 @@
         <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>61</v>
@@ -7295,22 +7259,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920244</v>
+        <v>24330051920220</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7318,22 +7282,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920396</v>
+        <v>24330051920226</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7344,19 +7308,19 @@
         <v>24330051920396</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7364,185 +7328,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920226</v>
+        <v>24330051920229</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920408</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920229</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920357</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920230</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920231</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920245</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24330051920246</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20241.xlsx
+++ b/grupos/1CV - Estadisticos 20241.xlsx
@@ -212,7 +212,7 @@
     <t>Ramírez Vargas Miranda Alejandra</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
+    <t>Breniz Camarillo Lysette</t>
   </si>
   <si>
     <t>Silva Villegas Mario</t>

--- a/grupos/1CV - Estadisticos 20241.xlsx
+++ b/grupos/1CV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="95">
   <si>
     <t>Materia</t>
   </si>
@@ -197,6 +197,9 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
@@ -206,6 +209,9 @@
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
+    <t>Desc Desc Desc</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -215,12 +221,6 @@
     <t>Breniz Camarillo Lysette</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -233,7 +233,10 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
   </si>
   <si>
     <t>BAUTISTA</t>
@@ -251,12 +254,18 @@
     <t>MORA</t>
   </si>
   <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>ZUNO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>CHAPARRO</t>
   </si>
   <si>
@@ -266,10 +275,13 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>DANIELA LILI</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ARELI CICLARI</t>
+  </si>
+  <si>
+    <t>ERIKA VALERIA</t>
   </si>
   <si>
     <t>LUZ ELENA</t>
@@ -284,7 +296,13 @@
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>BRENDA</t>
+    <t>MARELY</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ALIN MARIEL</t>
   </si>
 </sst>
 </file>
@@ -830,7 +848,7 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -851,7 +869,7 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -878,7 +896,7 @@
         <v>-1</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA4">
         <v>7</v>
@@ -899,7 +917,7 @@
         <v>7</v>
       </c>
       <c r="AG4">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:33">
@@ -931,7 +949,7 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>5</v>
@@ -952,7 +970,7 @@
         <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -979,7 +997,7 @@
         <v>-1</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA5">
         <v>5</v>
@@ -1000,7 +1018,7 @@
         <v>5</v>
       </c>
       <c r="AG5">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:33">
@@ -1032,7 +1050,7 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>7</v>
@@ -1053,7 +1071,7 @@
         <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1080,7 +1098,7 @@
         <v>-1</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA6">
         <v>6</v>
@@ -1133,7 +1151,7 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -1154,7 +1172,7 @@
         <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1181,7 +1199,7 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>7</v>
@@ -1234,7 +1252,7 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>7</v>
@@ -1255,7 +1273,7 @@
         <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1282,7 +1300,7 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA8">
         <v>7</v>
@@ -1303,7 +1321,7 @@
         <v>5</v>
       </c>
       <c r="AG8">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:33">
@@ -1335,7 +1353,7 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>7</v>
@@ -1356,7 +1374,7 @@
         <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1404,7 +1422,7 @@
         <v>5</v>
       </c>
       <c r="AG9">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:33">
@@ -1436,7 +1454,7 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>8</v>
@@ -1457,7 +1475,7 @@
         <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1484,7 +1502,7 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>9</v>
@@ -1537,7 +1555,7 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
         <v>8</v>
@@ -1558,7 +1576,7 @@
         <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1585,7 +1603,7 @@
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA11">
         <v>8</v>
@@ -1638,7 +1656,7 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>8</v>
@@ -1659,7 +1677,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1686,7 +1704,7 @@
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <v>8</v>
@@ -1739,7 +1757,7 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>8</v>
@@ -1760,7 +1778,7 @@
         <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1840,7 +1858,7 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>6</v>
@@ -1861,7 +1879,7 @@
         <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1888,7 +1906,7 @@
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>6</v>
@@ -1941,7 +1959,7 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>7</v>
@@ -1962,7 +1980,7 @@
         <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2042,7 +2060,7 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>7</v>
@@ -2063,7 +2081,7 @@
         <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2090,7 +2108,7 @@
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA16">
         <v>7</v>
@@ -2143,7 +2161,7 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>5</v>
@@ -2164,7 +2182,7 @@
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2191,7 +2209,7 @@
         <v>-1</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>5</v>
@@ -2244,7 +2262,7 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>5</v>
@@ -2265,7 +2283,7 @@
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2313,7 +2331,7 @@
         <v>5</v>
       </c>
       <c r="AG18">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:33">
@@ -2345,7 +2363,7 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>5</v>
@@ -2366,7 +2384,7 @@
         <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2393,7 +2411,7 @@
         <v>-1</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA19">
         <v>5</v>
@@ -2414,7 +2432,7 @@
         <v>5</v>
       </c>
       <c r="AG19">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:33">
@@ -2446,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>6</v>
@@ -2467,7 +2485,7 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2494,7 +2512,7 @@
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>6</v>
@@ -2547,7 +2565,7 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>8</v>
@@ -2568,7 +2586,7 @@
         <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2595,7 +2613,7 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA21">
         <v>8</v>
@@ -2648,7 +2666,7 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>10</v>
@@ -2669,7 +2687,7 @@
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2696,7 +2714,7 @@
         <v>-1</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2749,7 +2767,7 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>6</v>
@@ -2770,7 +2788,7 @@
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2797,7 +2815,7 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA23">
         <v>7</v>
@@ -2850,7 +2868,7 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
         <v>7</v>
@@ -2871,7 +2889,7 @@
         <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2898,7 +2916,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>7</v>
@@ -2951,7 +2969,7 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
         <v>7</v>
@@ -2972,7 +2990,7 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2999,7 +3017,7 @@
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -3052,7 +3070,7 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>8</v>
@@ -3073,7 +3091,7 @@
         <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3100,7 +3118,7 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA26">
         <v>8</v>
@@ -3153,7 +3171,7 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>5</v>
@@ -3174,7 +3192,7 @@
         <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3222,7 +3240,7 @@
         <v>5</v>
       </c>
       <c r="AG27">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:33">
@@ -3254,7 +3272,7 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>6</v>
@@ -3275,7 +3293,7 @@
         <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3323,7 +3341,7 @@
         <v>6</v>
       </c>
       <c r="AG28">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:33">
@@ -3355,7 +3373,7 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
         <v>7</v>
@@ -3376,7 +3394,7 @@
         <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3403,7 +3421,7 @@
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA29">
         <v>8</v>
@@ -3456,7 +3474,7 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>7</v>
@@ -3477,7 +3495,7 @@
         <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3557,7 +3575,7 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>10</v>
@@ -3578,7 +3596,7 @@
         <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3605,7 +3623,7 @@
         <v>-1</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>10</v>
@@ -3658,7 +3676,7 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>6</v>
@@ -3679,7 +3697,7 @@
         <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3706,7 +3724,7 @@
         <v>-1</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>6</v>
@@ -3759,7 +3777,7 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
         <v>8</v>
@@ -3780,7 +3798,7 @@
         <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3807,7 +3825,7 @@
         <v>-1</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA33">
         <v>8</v>
@@ -3860,7 +3878,7 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>6</v>
@@ -3881,7 +3899,7 @@
         <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3908,7 +3926,7 @@
         <v>-1</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>5</v>
@@ -3961,7 +3979,7 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
         <v>8</v>
@@ -3982,7 +4000,7 @@
         <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -4062,7 +4080,7 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <v>6</v>
@@ -4083,7 +4101,7 @@
         <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -4110,7 +4128,7 @@
         <v>-1</v>
       </c>
       <c r="Z36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA36">
         <v>7</v>
@@ -4297,7 +4315,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -4318,10 +4336,10 @@
         <v>97.5</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R4">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -4342,7 +4360,7 @@
         <v>97.5</v>
       </c>
       <c r="Y4">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -4374,7 +4392,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K5">
         <v>100</v>
@@ -4395,10 +4413,10 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4419,7 +4437,7 @@
         <v>100</v>
       </c>
       <c r="Y5">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -4451,7 +4469,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -4472,10 +4490,10 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -4496,7 +4514,7 @@
         <v>100</v>
       </c>
       <c r="Y6">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -4605,7 +4623,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -4626,10 +4644,10 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -4650,7 +4668,7 @@
         <v>100</v>
       </c>
       <c r="Y8">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -4682,7 +4700,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -4703,10 +4721,10 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="R9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4727,7 +4745,7 @@
         <v>100</v>
       </c>
       <c r="Y9">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -4836,7 +4854,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -4857,10 +4875,10 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -4881,7 +4899,7 @@
         <v>100</v>
       </c>
       <c r="Y11">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -4934,7 +4952,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -4958,7 +4976,7 @@
         <v>100</v>
       </c>
       <c r="Y12">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -5144,7 +5162,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -5165,10 +5183,10 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -5189,7 +5207,7 @@
         <v>100</v>
       </c>
       <c r="Y15">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -5298,7 +5316,7 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -5322,7 +5340,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -5375,7 +5393,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -5396,10 +5414,10 @@
         <v>50</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R18">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -5420,7 +5438,7 @@
         <v>50</v>
       </c>
       <c r="Y18">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -5452,7 +5470,7 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -5473,10 +5491,10 @@
         <v>50</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -5497,7 +5515,7 @@
         <v>50</v>
       </c>
       <c r="Y19">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -5529,7 +5547,7 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="K20">
         <v>100</v>
@@ -5550,10 +5568,10 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R20">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -5574,7 +5592,7 @@
         <v>100</v>
       </c>
       <c r="Y20">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -5627,7 +5645,7 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5651,7 +5669,7 @@
         <v>100</v>
       </c>
       <c r="Y21">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -5837,7 +5855,7 @@
         <v>100</v>
       </c>
       <c r="J24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -5861,7 +5879,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -6089,7 +6107,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R27">
         <v>80</v>
@@ -6113,7 +6131,7 @@
         <v>100</v>
       </c>
       <c r="Y27">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -6166,7 +6184,7 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R28">
         <v>70</v>
@@ -6190,7 +6208,7 @@
         <v>100</v>
       </c>
       <c r="Y28">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -6243,7 +6261,7 @@
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -6267,7 +6285,7 @@
         <v>100</v>
       </c>
       <c r="Y29">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -6299,7 +6317,7 @@
         <v>100</v>
       </c>
       <c r="J30">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -6323,7 +6341,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -6376,7 +6394,7 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -6400,7 +6418,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -6453,7 +6471,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -6477,7 +6495,7 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -6530,7 +6548,7 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -6551,10 +6569,10 @@
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R33">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -6575,7 +6593,7 @@
         <v>100</v>
       </c>
       <c r="Y33">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -6607,7 +6625,7 @@
         <v>100</v>
       </c>
       <c r="J34">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -6628,10 +6646,10 @@
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R34">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S34">
         <v>100</v>
@@ -6652,7 +6670,7 @@
         <v>100</v>
       </c>
       <c r="Y34">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -6705,7 +6723,7 @@
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R35">
         <v>100</v>
@@ -6729,7 +6747,7 @@
         <v>100</v>
       </c>
       <c r="Y35">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -6761,7 +6779,7 @@
         <v>100</v>
       </c>
       <c r="J36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K36">
         <v>100</v>
@@ -6782,10 +6800,10 @@
         <v>100</v>
       </c>
       <c r="Q36">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -6806,7 +6824,7 @@
         <v>100</v>
       </c>
       <c r="Y36">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -6863,7 +6881,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
@@ -6872,16 +6890,16 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>69.7</v>
+        <v>63.6</v>
       </c>
       <c r="G2" s="2">
-        <v>30.3</v>
+        <v>36.4</v>
       </c>
       <c r="H2">
         <v>6.6</v>
@@ -6895,7 +6913,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -6904,19 +6922,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2">
-        <v>75.8</v>
+        <v>69.7</v>
       </c>
       <c r="G3" s="2">
-        <v>24.2</v>
+        <v>30.3</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6927,7 +6945,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -6948,7 +6966,7 @@
         <v>24.2</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6959,7 +6977,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -6968,19 +6986,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2">
-        <v>78.8</v>
+        <v>75.8</v>
       </c>
       <c r="G5" s="2">
-        <v>21.2</v>
+        <v>24.2</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6991,7 +7009,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -7000,19 +7018,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2">
-        <v>78.8</v>
+        <v>75.8</v>
       </c>
       <c r="G6" s="2">
-        <v>21.2</v>
+        <v>24.2</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7023,7 +7041,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
@@ -7032,19 +7050,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2">
-        <v>81.8</v>
+        <v>78.8</v>
       </c>
       <c r="G7" s="2">
-        <v>18.2</v>
+        <v>21.2</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7055,7 +7073,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>65</v>
@@ -7064,19 +7082,19 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2">
-        <v>81.8</v>
+        <v>78.8</v>
       </c>
       <c r="G8" s="2">
-        <v>18.2</v>
+        <v>21.2</v>
       </c>
       <c r="H8">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7087,7 +7105,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>66</v>
@@ -7096,19 +7114,19 @@
         <v>33</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F9" s="2">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="G9" s="2">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -7158,7 +7176,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7190,22 +7208,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920330</v>
+        <v>24330051920217</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7213,22 +7231,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920330</v>
+        <v>24330051920217</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7236,22 +7254,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920244</v>
+        <v>24330051920238</v>
       </c>
       <c r="B4" t="s">
         <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7259,19 +7277,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920220</v>
+        <v>24330051920238</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>60</v>
@@ -7282,22 +7300,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920226</v>
+        <v>24330051920244</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7305,22 +7323,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920396</v>
+        <v>24330051920220</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7328,24 +7346,116 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920229</v>
+        <v>24330051920226</v>
       </c>
       <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>24330051920396</v>
+      </c>
+      <c r="B9" t="s">
         <v>76</v>
       </c>
-      <c r="C8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8">
+      <c r="C9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920228</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920230</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920246</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20241.xlsx
+++ b/grupos/1CV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="103">
   <si>
     <t>Materia</t>
   </si>
@@ -233,6 +233,15 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
@@ -260,6 +269,12 @@
     <t>ZUNO</t>
   </si>
   <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -276,6 +291,15 @@
   </si>
   <si>
     <t>FLORES</t>
+  </si>
+  <si>
+    <t>YARETZY NAOMI</t>
+  </si>
+  <si>
+    <t>ANGEL ISMAEL</t>
+  </si>
+  <si>
+    <t>DANIELA LILI</t>
   </si>
   <si>
     <t>ERIKA VALERIA</t>
@@ -6443,7 +6467,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6475,22 +6499,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920238</v>
+        <v>24330051920247</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6498,22 +6522,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920238</v>
+        <v>24330051920247</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6521,22 +6545,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920217</v>
+        <v>24330051920247</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6544,16 +6568,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920244</v>
+        <v>24330051920247</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -6567,22 +6591,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920220</v>
+        <v>24330051920239</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6590,22 +6614,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920226</v>
+        <v>24330051920239</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6613,22 +6637,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920396</v>
+        <v>24330051920239</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6636,22 +6660,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920228</v>
+        <v>24330051920239</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
         <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6659,13 +6683,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920230</v>
+        <v>24330051920330</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
         <v>93</v>
@@ -6682,24 +6706,277 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920246</v>
+        <v>24330051920330</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
         <v>85</v>
       </c>
       <c r="D11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920330</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920238</v>
+      </c>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" t="s">
         <v>94</v>
       </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920238</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>24330051920217</v>
+      </c>
+      <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
         <v>59</v>
       </c>
-      <c r="G11">
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920244</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>24330051920220</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920226</v>
+      </c>
+      <c r="B18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>24330051920396</v>
+      </c>
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920228</v>
+      </c>
+      <c r="B20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920230</v>
+      </c>
+      <c r="B21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920246</v>
+      </c>
+      <c r="B22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20241.xlsx
+++ b/grupos/1CV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="101">
   <si>
     <t>Materia</t>
   </si>
@@ -206,18 +206,18 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Ramírez Vargas Miranda Alejandra</t>
+  </si>
+  <si>
+    <t>Breniz Camarillo Lysette</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Ramírez Vargas Miranda Alejandra</t>
-  </si>
-  <si>
-    <t>Breniz Camarillo Lysette</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -233,33 +233,30 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>ANGUIANO</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
     <t>LEYVA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MORA</t>
   </si>
   <si>
@@ -269,15 +266,18 @@
     <t>ZUNO</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>PINO</t>
   </si>
   <si>
     <t>BONILLA</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>CABRERA</t>
   </si>
   <si>
@@ -287,37 +287,31 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>MAYRIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANIELA LILI</t>
+  </si>
+  <si>
     <t>YARETZY NAOMI</t>
   </si>
   <si>
+    <t>ERIKA VALERIA</t>
+  </si>
+  <si>
     <t>ANGEL ISMAEL</t>
   </si>
   <si>
-    <t>DANIELA LILI</t>
-  </si>
-  <si>
-    <t>ERIKA VALERIA</t>
-  </si>
-  <si>
     <t>ARELI CICLARI</t>
   </si>
   <si>
-    <t>LUZ ELENA</t>
-  </si>
-  <si>
     <t>MAYKA XIMENA</t>
   </si>
   <si>
     <t>EUNICE GUADALUPE</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
   </si>
   <si>
     <t>MARELY</t>
@@ -877,16 +871,16 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -901,7 +895,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>10</v>
@@ -966,16 +960,16 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1055,16 +1049,16 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1085,7 +1079,7 @@
         <v>9</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6">
         <v>9</v>
@@ -1144,16 +1138,16 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1233,16 +1227,16 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1322,16 +1316,16 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1411,16 +1405,16 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1432,10 +1426,10 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>10</v>
@@ -1500,16 +1494,16 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1521,7 +1515,7 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1589,16 +1583,16 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1678,16 +1672,16 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1767,16 +1761,16 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1856,16 +1850,16 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1945,16 +1939,16 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -2034,16 +2028,16 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2055,7 +2049,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -2123,16 +2117,16 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2212,16 +2206,16 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2301,16 +2295,16 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2325,7 +2319,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>7</v>
@@ -2390,16 +2384,16 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2414,7 +2408,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>9</v>
@@ -2479,16 +2473,16 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2503,13 +2497,13 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>7</v>
       </c>
       <c r="AA22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB22">
         <v>7</v>
@@ -2541,7 +2535,7 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I23">
         <v>5</v>
@@ -2568,16 +2562,16 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2598,13 +2592,13 @@
         <v>8</v>
       </c>
       <c r="AA23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>8</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2657,16 +2651,16 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2746,16 +2740,16 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2776,7 +2770,7 @@
         <v>9</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB25">
         <v>8</v>
@@ -2835,16 +2829,16 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2856,7 +2850,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2865,7 +2859,7 @@
         <v>10</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB26">
         <v>10</v>
@@ -2924,16 +2918,16 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -2945,7 +2939,7 @@
         <v>5</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -2954,7 +2948,7 @@
         <v>6</v>
       </c>
       <c r="AA27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB27">
         <v>5</v>
@@ -3013,16 +3007,16 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -3034,7 +3028,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -3043,7 +3037,7 @@
         <v>6</v>
       </c>
       <c r="AA28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB28">
         <v>6</v>
@@ -3102,16 +3096,16 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3191,16 +3185,16 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3212,7 +3206,7 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3221,7 +3215,7 @@
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB30">
         <v>7</v>
@@ -3280,16 +3274,16 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3310,7 +3304,7 @@
         <v>5</v>
       </c>
       <c r="AA31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB31">
         <v>7</v>
@@ -3369,16 +3363,16 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3393,13 +3387,13 @@
         <v>6</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z32">
         <v>9</v>
       </c>
       <c r="AA32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB32">
         <v>7</v>
@@ -3458,16 +3452,16 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3488,7 +3482,7 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB33">
         <v>6</v>
@@ -3547,16 +3541,16 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3568,16 +3562,16 @@
         <v>7</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z34">
         <v>5</v>
       </c>
       <c r="AA34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB34">
         <v>6</v>
@@ -3636,16 +3630,16 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3725,16 +3719,16 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>-1</v>
@@ -3755,7 +3749,7 @@
         <v>6</v>
       </c>
       <c r="AA36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB36">
         <v>8</v>
@@ -3939,7 +3933,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>95.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S4">
         <v>96.7</v>
@@ -4004,16 +3998,16 @@
         <v>50</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R5">
-        <v>45.5</v>
+        <v>31.3</v>
       </c>
       <c r="S5">
         <v>50</v>
       </c>
       <c r="T5">
-        <v>88.09999999999999</v>
+        <v>59.7</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -4075,13 +4069,13 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="S6">
         <v>93.3</v>
       </c>
       <c r="T6">
-        <v>90.5</v>
+        <v>93.5</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -4143,7 +4137,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -4211,13 +4205,13 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>84.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="S8">
         <v>83.3</v>
       </c>
       <c r="T8">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U8">
         <v>65.59999999999999</v>
@@ -4279,13 +4273,13 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>84.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="S9">
         <v>80</v>
       </c>
       <c r="T9">
-        <v>95.2</v>
+        <v>93.5</v>
       </c>
       <c r="U9">
         <v>65.59999999999999</v>
@@ -4347,7 +4341,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -4415,13 +4409,13 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>86.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="S11">
         <v>93.3</v>
       </c>
       <c r="T11">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U11">
         <v>87.5</v>
@@ -4483,7 +4477,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S12">
         <v>96.7</v>
@@ -4551,7 +4545,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S13">
         <v>96.7</v>
@@ -4687,13 +4681,13 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S15">
         <v>93.3</v>
       </c>
       <c r="T15">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U15">
         <v>93.8</v>
@@ -4755,7 +4749,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="S16">
         <v>96.7</v>
@@ -4823,13 +4817,13 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S17">
         <v>96.7</v>
       </c>
       <c r="T17">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U17">
         <v>100</v>
@@ -4888,16 +4882,16 @@
         <v>65</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R18">
-        <v>68.2</v>
+        <v>46.9</v>
       </c>
       <c r="S18">
         <v>90</v>
       </c>
       <c r="T18">
-        <v>92.90000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="U18">
         <v>53.1</v>
@@ -4956,16 +4950,16 @@
         <v>90</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R19">
-        <v>75</v>
+        <v>51.6</v>
       </c>
       <c r="S19">
         <v>96.7</v>
       </c>
       <c r="T19">
-        <v>97.59999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="U19">
         <v>93.8</v>
@@ -5027,7 +5021,7 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S20">
         <v>80</v>
@@ -5095,7 +5089,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>84.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="S21">
         <v>90</v>
@@ -5163,7 +5157,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="S22">
         <v>83.3</v>
@@ -5231,7 +5225,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>95.5</v>
+        <v>92.2</v>
       </c>
       <c r="S23">
         <v>96.7</v>
@@ -5299,7 +5293,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S24">
         <v>96.7</v>
@@ -5367,7 +5361,7 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S25">
         <v>96.7</v>
@@ -5435,7 +5429,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -5503,13 +5497,13 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S27">
         <v>76.7</v>
       </c>
       <c r="T27">
-        <v>85.7</v>
+        <v>90.3</v>
       </c>
       <c r="U27">
         <v>78.09999999999999</v>
@@ -5571,13 +5565,13 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="S28">
         <v>80</v>
       </c>
       <c r="T28">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U28">
         <v>93.8</v>
@@ -5639,7 +5633,7 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S29">
         <v>93.3</v>
@@ -5707,7 +5701,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>97.7</v>
+        <v>93.8</v>
       </c>
       <c r="S30">
         <v>96.7</v>
@@ -5775,13 +5769,13 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S31">
         <v>86.7</v>
       </c>
       <c r="T31">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U31">
         <v>90.59999999999999</v>
@@ -5843,13 +5837,13 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="S32">
         <v>90</v>
       </c>
       <c r="T32">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U32">
         <v>96.90000000000001</v>
@@ -5911,13 +5905,13 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S33">
         <v>86.7</v>
       </c>
       <c r="T33">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U33">
         <v>90.59999999999999</v>
@@ -5979,13 +5973,13 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S34">
         <v>90</v>
       </c>
       <c r="T34">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U34">
         <v>84.40000000000001</v>
@@ -6047,7 +6041,7 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>97.7</v>
+        <v>93.8</v>
       </c>
       <c r="S35">
         <v>93.3</v>
@@ -6115,13 +6109,13 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S36">
         <v>83.3</v>
       </c>
       <c r="T36">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U36">
         <v>93.8</v>
@@ -6237,7 +6231,7 @@
         <v>30.3</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6257,19 +6251,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>75.8</v>
+        <v>78.8</v>
       </c>
       <c r="G4" s="2">
-        <v>24.2</v>
+        <v>21.2</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6280,7 +6274,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -6289,19 +6283,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>75.8</v>
+        <v>78.8</v>
       </c>
       <c r="G5" s="2">
-        <v>24.2</v>
+        <v>21.2</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6312,7 +6306,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -6321,19 +6315,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>78.8</v>
+        <v>81.8</v>
       </c>
       <c r="G6" s="2">
-        <v>21.2</v>
+        <v>18.2</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6344,7 +6338,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
@@ -6353,19 +6347,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>78.8</v>
+        <v>84.8</v>
       </c>
       <c r="G7" s="2">
-        <v>21.2</v>
+        <v>15.2</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6376,7 +6370,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>65</v>
@@ -6385,19 +6379,19 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>81.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>18.2</v>
+        <v>9.1</v>
       </c>
       <c r="H8">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6467,7 +6461,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6499,16 +6493,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920247</v>
+        <v>24330051920389</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6522,19 +6516,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920247</v>
+        <v>24330051920389</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>63</v>
@@ -6545,22 +6539,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920247</v>
+        <v>24330051920389</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6568,10 +6562,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920247</v>
+        <v>24330051920330</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
         <v>83</v>
@@ -6580,10 +6574,10 @@
         <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6591,22 +6585,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920239</v>
+        <v>24330051920330</v>
       </c>
       <c r="B6" t="s">
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6614,22 +6608,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920239</v>
+        <v>24330051920330</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6637,10 +6631,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920239</v>
+        <v>24330051920247</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
         <v>84</v>
@@ -6649,10 +6643,10 @@
         <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6660,10 +6654,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920239</v>
+        <v>24330051920247</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
         <v>84</v>
@@ -6672,10 +6666,10 @@
         <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6683,22 +6677,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920330</v>
+        <v>24330051920238</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
         <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6706,22 +6700,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920330</v>
+        <v>24330051920238</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
         <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6729,22 +6723,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920330</v>
+        <v>24330051920239</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
         <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6752,10 +6746,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920238</v>
+        <v>24330051920239</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
         <v>85</v>
@@ -6764,10 +6758,10 @@
         <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6775,22 +6769,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920238</v>
+        <v>24330051920217</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6798,22 +6792,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920217</v>
+        <v>24330051920220</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -6821,22 +6815,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920244</v>
+        <v>24330051920226</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -6844,22 +6838,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920220</v>
+        <v>24330051920228</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -6867,22 +6861,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920226</v>
+        <v>24330051920230</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
         <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E18" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -6890,93 +6884,24 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920396</v>
+        <v>24330051920246</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
         <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920228</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920230</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" t="s">
-        <v>101</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>24330051920246</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20241.xlsx
+++ b/grupos/1CV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -200,6 +200,9 @@
     <t>Silva Villegas Mario</t>
   </si>
   <si>
+    <t>Breniz Camarillo Lysette</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
@@ -209,9 +212,6 @@
     <t>Ramírez Vargas Miranda Alejandra</t>
   </si>
   <si>
-    <t>Breniz Camarillo Lysette</t>
-  </si>
-  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
@@ -233,45 +233,42 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
     <t>ZUNO</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>PINO</t>
   </si>
   <si>
@@ -290,34 +287,31 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>DANIELA LILI</t>
+  </si>
+  <si>
     <t>MAYRIN GUADALUPE</t>
   </si>
   <si>
-    <t>DANIELA LILI</t>
-  </si>
-  <si>
     <t>YARETZY NAOMI</t>
   </si>
   <si>
+    <t>ANGEL ISMAEL</t>
+  </si>
+  <si>
+    <t>ARELI CICLARI</t>
+  </si>
+  <si>
+    <t>MAYKA XIMENA</t>
+  </si>
+  <si>
+    <t>MARELY</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
     <t>ERIKA VALERIA</t>
-  </si>
-  <si>
-    <t>ANGEL ISMAEL</t>
-  </si>
-  <si>
-    <t>ARELI CICLARI</t>
-  </si>
-  <si>
-    <t>MAYKA XIMENA</t>
-  </si>
-  <si>
-    <t>EUNICE GUADALUPE</t>
-  </si>
-  <si>
-    <t>MARELY</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
   </si>
   <si>
     <t>ALIN MARIEL</t>
@@ -883,10 +877,10 @@
         <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -904,7 +898,7 @@
         <v>6</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC4">
         <v>7</v>
@@ -972,10 +966,10 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>5</v>
@@ -1061,10 +1055,10 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1150,10 +1144,10 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1171,7 +1165,7 @@
         <v>10</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>7</v>
@@ -1239,10 +1233,10 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1328,10 +1322,10 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1417,10 +1411,10 @@
         <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1506,10 +1500,10 @@
         <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1527,7 +1521,7 @@
         <v>6</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC11">
         <v>6</v>
@@ -1595,10 +1589,10 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1616,7 +1610,7 @@
         <v>7</v>
       </c>
       <c r="AB12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC12">
         <v>9</v>
@@ -1684,10 +1678,10 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1773,10 +1767,10 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1797,7 +1791,7 @@
         <v>8</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1862,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1886,7 +1880,7 @@
         <v>9</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1951,10 +1945,10 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -2040,10 +2034,10 @@
         <v>8</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2129,10 +2123,10 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2218,10 +2212,10 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2307,10 +2301,10 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2331,7 +2325,7 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2396,10 +2390,10 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2485,10 +2479,10 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2506,7 +2500,7 @@
         <v>6</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>6</v>
@@ -2574,10 +2568,10 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2595,10 +2589,10 @@
         <v>8</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2663,10 +2657,10 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2752,10 +2746,10 @@
         <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2841,10 +2835,10 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2930,10 +2924,10 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -3019,10 +3013,10 @@
         <v>8</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -3040,7 +3034,7 @@
         <v>6</v>
       </c>
       <c r="AB28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC28">
         <v>6</v>
@@ -3108,10 +3102,10 @@
         <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -3197,10 +3191,10 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -3218,10 +3212,10 @@
         <v>8</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3286,10 +3280,10 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>7</v>
@@ -3307,10 +3301,10 @@
         <v>7</v>
       </c>
       <c r="AB31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3375,10 +3369,10 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>8</v>
@@ -3396,7 +3390,7 @@
         <v>7</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC32">
         <v>7</v>
@@ -3464,10 +3458,10 @@
         <v>5</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W33">
         <v>5</v>
@@ -3485,7 +3479,7 @@
         <v>6</v>
       </c>
       <c r="AB33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC33">
         <v>5</v>
@@ -3553,10 +3547,10 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -3574,7 +3568,7 @@
         <v>6</v>
       </c>
       <c r="AB34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC34">
         <v>5</v>
@@ -3642,10 +3636,10 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -3666,7 +3660,7 @@
         <v>10</v>
       </c>
       <c r="AC35">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3731,10 +3725,10 @@
         <v>6</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3752,7 +3746,7 @@
         <v>7</v>
       </c>
       <c r="AB36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC36">
         <v>6</v>
@@ -3942,10 +3936,10 @@
         <v>100</v>
       </c>
       <c r="U4">
-        <v>93.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="V4">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4010,10 +4004,10 @@
         <v>59.7</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V5">
-        <v>100</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4078,10 +4072,10 @@
         <v>93.5</v>
       </c>
       <c r="U6">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V6">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4214,7 +4208,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="U8">
-        <v>65.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4282,7 +4276,7 @@
         <v>93.5</v>
       </c>
       <c r="U9">
-        <v>65.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -4350,7 +4344,7 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -4418,7 +4412,7 @@
         <v>96.8</v>
       </c>
       <c r="U11">
-        <v>87.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -4486,7 +4480,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -4554,7 +4548,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4622,7 +4616,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -4690,7 +4684,7 @@
         <v>96.8</v>
       </c>
       <c r="U15">
-        <v>93.8</v>
+        <v>95.7</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -4758,7 +4752,7 @@
         <v>100</v>
       </c>
       <c r="U16">
-        <v>96.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -4894,10 +4888,10 @@
         <v>62.9</v>
       </c>
       <c r="U18">
-        <v>53.1</v>
+        <v>38.3</v>
       </c>
       <c r="V18">
-        <v>50</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4962,10 +4956,10 @@
         <v>66.09999999999999</v>
       </c>
       <c r="U19">
-        <v>93.8</v>
+        <v>66</v>
       </c>
       <c r="V19">
-        <v>50</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5030,7 +5024,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>84.40000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -5098,7 +5092,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -5166,7 +5160,7 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -5302,7 +5296,7 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>93.8</v>
+        <v>95.7</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -5506,7 +5500,7 @@
         <v>90.3</v>
       </c>
       <c r="U27">
-        <v>78.09999999999999</v>
+        <v>55.3</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -5574,7 +5568,7 @@
         <v>95.2</v>
       </c>
       <c r="U28">
-        <v>93.8</v>
+        <v>66</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5642,7 +5636,7 @@
         <v>100</v>
       </c>
       <c r="U29">
-        <v>96.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -5710,7 +5704,7 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>90.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -5778,7 +5772,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="U31">
-        <v>90.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -5846,7 +5840,7 @@
         <v>96.8</v>
       </c>
       <c r="U32">
-        <v>96.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -5914,7 +5908,7 @@
         <v>96.8</v>
       </c>
       <c r="U33">
-        <v>90.59999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -5982,7 +5976,7 @@
         <v>96.8</v>
       </c>
       <c r="U34">
-        <v>84.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="V34">
         <v>100</v>
@@ -6050,7 +6044,7 @@
         <v>100</v>
       </c>
       <c r="U35">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V35">
         <v>100</v>
@@ -6118,7 +6112,7 @@
         <v>95.2</v>
       </c>
       <c r="U36">
-        <v>93.8</v>
+        <v>87.2</v>
       </c>
       <c r="V36">
         <v>100</v>
@@ -6210,7 +6204,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -6219,19 +6213,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2">
-        <v>69.7</v>
+        <v>72.7</v>
       </c>
       <c r="G3" s="2">
-        <v>30.3</v>
+        <v>27.3</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6242,7 +6236,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -6251,19 +6245,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2">
-        <v>78.8</v>
+        <v>75.8</v>
       </c>
       <c r="G4" s="2">
-        <v>21.2</v>
+        <v>24.2</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6274,7 +6268,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -6295,7 +6289,7 @@
         <v>21.2</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6306,7 +6300,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -6315,19 +6309,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>81.8</v>
+        <v>78.8</v>
       </c>
       <c r="G6" s="2">
-        <v>18.2</v>
+        <v>21.2</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6461,7 +6455,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6493,16 +6487,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920389</v>
+        <v>24330051920330</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6516,19 +6510,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920389</v>
+        <v>24330051920330</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>63</v>
@@ -6539,19 +6533,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920389</v>
+        <v>24330051920330</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>60</v>
@@ -6565,19 +6559,19 @@
         <v>24330051920330</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6585,22 +6579,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920330</v>
+        <v>24330051920389</v>
       </c>
       <c r="B6" t="s">
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6608,19 +6602,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920330</v>
+        <v>24330051920389</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>60</v>
@@ -6631,22 +6625,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920247</v>
+        <v>24330051920389</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6660,16 +6654,16 @@
         <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6677,19 +6671,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920238</v>
+        <v>24330051920247</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
         <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>62</v>
@@ -6700,19 +6694,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920238</v>
+        <v>24330051920247</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
         <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>60</v>
@@ -6726,19 +6720,19 @@
         <v>24330051920239</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6749,16 +6743,16 @@
         <v>24330051920239</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>60</v>
@@ -6769,22 +6763,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920217</v>
+        <v>24330051920239</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6792,22 +6786,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920220</v>
+        <v>24330051920217</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -6815,22 +6809,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920226</v>
+        <v>24330051920220</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -6841,13 +6835,13 @@
         <v>24330051920228</v>
       </c>
       <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
         <v>79</v>
       </c>
-      <c r="C17" t="s">
-        <v>74</v>
-      </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
         <v>5</v>
@@ -6864,13 +6858,13 @@
         <v>24330051920230</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
@@ -6884,24 +6878,47 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
+        <v>24330051920238</v>
+      </c>
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
         <v>24330051920246</v>
       </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="B20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
         <v>59</v>
       </c>
-      <c r="G19">
+      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20241.xlsx
+++ b/grupos/1CV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="89">
   <si>
     <t>Materia</t>
   </si>
@@ -197,15 +197,15 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Breniz Camarillo Lysette</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
-    <t>Breniz Camarillo Lysette</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
@@ -245,21 +245,9 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>ZUNO</t>
   </si>
   <si>
@@ -275,15 +263,9 @@
     <t>BONILLA</t>
   </si>
   <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
     <t>CHAPARRO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -299,19 +281,7 @@
     <t>ANGEL ISMAEL</t>
   </si>
   <si>
-    <t>ARELI CICLARI</t>
-  </si>
-  <si>
     <t>MAYKA XIMENA</t>
-  </si>
-  <si>
-    <t>MARELY</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ERIKA VALERIA</t>
   </si>
   <si>
     <t>ALIN MARIEL</t>
@@ -862,7 +832,7 @@
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>7</v>
@@ -871,7 +841,7 @@
         <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -883,7 +853,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -892,7 +862,7 @@
         <v>7</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA4">
         <v>6</v>
@@ -951,7 +921,7 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>5</v>
@@ -960,7 +930,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>5</v>
@@ -1040,7 +1010,7 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>7</v>
@@ -1049,7 +1019,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1129,7 +1099,7 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
         <v>7</v>
@@ -1138,7 +1108,7 @@
         <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1159,7 +1129,7 @@
         <v>8</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA7">
         <v>10</v>
@@ -1218,7 +1188,7 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>6</v>
@@ -1227,7 +1197,7 @@
         <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -1307,7 +1277,7 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -1316,7 +1286,7 @@
         <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -1396,7 +1366,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1405,7 +1375,7 @@
         <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1426,7 +1396,7 @@
         <v>7</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA10">
         <v>9</v>
@@ -1485,7 +1455,7 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>7</v>
@@ -1494,7 +1464,7 @@
         <v>4</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>6</v>
@@ -1506,7 +1476,7 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1574,7 +1544,7 @@
         <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -1583,7 +1553,7 @@
         <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1663,7 +1633,7 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
         <v>8</v>
@@ -1672,7 +1642,7 @@
         <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1752,7 +1722,7 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>6</v>
@@ -1761,7 +1731,7 @@
         <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1841,7 +1811,7 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1850,7 +1820,7 @@
         <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1871,7 +1841,7 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>10</v>
@@ -1930,7 +1900,7 @@
         <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>7</v>
@@ -1939,7 +1909,7 @@
         <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1951,7 +1921,7 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -2019,7 +1989,7 @@
         <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>8</v>
@@ -2028,7 +1998,7 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -2108,7 +2078,7 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -2117,7 +2087,7 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>5</v>
@@ -2197,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>5</v>
@@ -2206,7 +2176,7 @@
         <v>4</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>5</v>
@@ -2286,7 +2256,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>6</v>
@@ -2295,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>8</v>
@@ -2375,7 +2345,7 @@
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
         <v>8</v>
@@ -2384,7 +2354,7 @@
         <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2396,7 +2366,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2405,7 +2375,7 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA21">
         <v>7</v>
@@ -2464,7 +2434,7 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -2473,7 +2443,7 @@
         <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>5</v>
@@ -2485,7 +2455,7 @@
         <v>6</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2494,7 +2464,7 @@
         <v>7</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <v>6</v>
@@ -2553,7 +2523,7 @@
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>7</v>
@@ -2562,7 +2532,7 @@
         <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -2574,7 +2544,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2642,7 +2612,7 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
         <v>7</v>
@@ -2651,7 +2621,7 @@
         <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2663,7 +2633,7 @@
         <v>6</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2731,7 +2701,7 @@
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>7</v>
@@ -2740,7 +2710,7 @@
         <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2820,7 +2790,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>7</v>
@@ -2829,7 +2799,7 @@
         <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2850,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA26">
         <v>9</v>
@@ -2909,7 +2879,7 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
         <v>8</v>
@@ -2918,7 +2888,7 @@
         <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2998,7 +2968,7 @@
         <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>7</v>
@@ -3007,7 +2977,7 @@
         <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
         <v>8</v>
@@ -3087,7 +3057,7 @@
         <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>7</v>
@@ -3096,7 +3066,7 @@
         <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -3108,7 +3078,7 @@
         <v>7</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -3176,7 +3146,7 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
         <v>7</v>
@@ -3185,7 +3155,7 @@
         <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>8</v>
@@ -3197,7 +3167,7 @@
         <v>5</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -3206,7 +3176,7 @@
         <v>7</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA30">
         <v>8</v>
@@ -3265,7 +3235,7 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>10</v>
@@ -3274,7 +3244,7 @@
         <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>8</v>
@@ -3286,7 +3256,7 @@
         <v>7</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3295,7 +3265,7 @@
         <v>8</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>7</v>
@@ -3354,7 +3324,7 @@
         <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -3363,7 +3333,7 @@
         <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
         <v>7</v>
@@ -3384,7 +3354,7 @@
         <v>7</v>
       </c>
       <c r="Z32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>7</v>
@@ -3443,7 +3413,7 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
         <v>8</v>
@@ -3452,7 +3422,7 @@
         <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>5</v>
@@ -3532,7 +3502,7 @@
         <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
         <v>7</v>
@@ -3541,7 +3511,7 @@
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T34">
         <v>5</v>
@@ -3553,7 +3523,7 @@
         <v>5</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>6</v>
@@ -3621,7 +3591,7 @@
         <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>8</v>
@@ -3630,7 +3600,7 @@
         <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>9</v>
@@ -3651,7 +3621,7 @@
         <v>8</v>
       </c>
       <c r="Z35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA35">
         <v>9</v>
@@ -3710,7 +3680,7 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
         <v>7</v>
@@ -3719,7 +3689,7 @@
         <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T36">
         <v>6</v>
@@ -3731,7 +3701,7 @@
         <v>6</v>
       </c>
       <c r="W36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X36">
         <v>7</v>
@@ -3740,7 +3710,7 @@
         <v>7</v>
       </c>
       <c r="Z36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA36">
         <v>7</v>
@@ -3921,7 +3891,7 @@
         <v>97.5</v>
       </c>
       <c r="P4">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3930,7 +3900,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="S4">
-        <v>96.7</v>
+        <v>93.8</v>
       </c>
       <c r="T4">
         <v>100</v>
@@ -3989,7 +3959,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="Q5">
         <v>66.7</v>
@@ -3998,7 +3968,7 @@
         <v>31.3</v>
       </c>
       <c r="S5">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="T5">
         <v>59.7</v>
@@ -4057,7 +4027,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4066,7 +4036,7 @@
         <v>92.2</v>
       </c>
       <c r="S6">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="T6">
         <v>93.5</v>
@@ -4193,7 +4163,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>85</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4202,7 +4172,7 @@
         <v>76.59999999999999</v>
       </c>
       <c r="S8">
-        <v>83.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="T8">
         <v>98.40000000000001</v>
@@ -4261,7 +4231,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>65</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -4270,7 +4240,7 @@
         <v>73.40000000000001</v>
       </c>
       <c r="S9">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="T9">
         <v>93.5</v>
@@ -4397,7 +4367,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4406,7 +4376,7 @@
         <v>82.8</v>
       </c>
       <c r="S11">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="T11">
         <v>96.8</v>
@@ -4465,7 +4435,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4474,7 +4444,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S12">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -4542,7 +4512,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S13">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -4669,7 +4639,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4678,7 +4648,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S15">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="T15">
         <v>96.8</v>
@@ -4746,7 +4716,7 @@
         <v>93.8</v>
       </c>
       <c r="S16">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -4805,7 +4775,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -4814,7 +4784,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S17">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="T17">
         <v>98.40000000000001</v>
@@ -4873,7 +4843,7 @@
         <v>50</v>
       </c>
       <c r="P18">
-        <v>65</v>
+        <v>40.6</v>
       </c>
       <c r="Q18">
         <v>66.7</v>
@@ -4882,7 +4852,7 @@
         <v>46.9</v>
       </c>
       <c r="S18">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="T18">
         <v>62.9</v>
@@ -4941,7 +4911,7 @@
         <v>50</v>
       </c>
       <c r="P19">
-        <v>90</v>
+        <v>81.3</v>
       </c>
       <c r="Q19">
         <v>66.7</v>
@@ -4950,7 +4920,7 @@
         <v>51.6</v>
       </c>
       <c r="S19">
-        <v>96.7</v>
+        <v>60.4</v>
       </c>
       <c r="T19">
         <v>66.09999999999999</v>
@@ -5009,7 +4979,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -5018,7 +4988,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S20">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -5077,7 +5047,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -5086,7 +5056,7 @@
         <v>87.5</v>
       </c>
       <c r="S21">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -5222,7 +5192,7 @@
         <v>92.2</v>
       </c>
       <c r="S23">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -5281,7 +5251,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -5290,7 +5260,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S24">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -5358,7 +5328,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S25">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T25">
         <v>100</v>
@@ -5485,7 +5455,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5494,7 +5464,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S27">
-        <v>76.7</v>
+        <v>83.3</v>
       </c>
       <c r="T27">
         <v>90.3</v>
@@ -5553,7 +5523,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5562,7 +5532,7 @@
         <v>92.2</v>
       </c>
       <c r="S28">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="T28">
         <v>95.2</v>
@@ -5630,7 +5600,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S29">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -5689,7 +5659,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5698,7 +5668,7 @@
         <v>93.8</v>
       </c>
       <c r="S30">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="T30">
         <v>100</v>
@@ -5757,7 +5727,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -5766,7 +5736,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S31">
-        <v>86.7</v>
+        <v>95.8</v>
       </c>
       <c r="T31">
         <v>98.40000000000001</v>
@@ -5825,7 +5795,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -5834,7 +5804,7 @@
         <v>95.3</v>
       </c>
       <c r="S32">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T32">
         <v>96.8</v>
@@ -5893,7 +5863,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -5902,7 +5872,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="S33">
-        <v>86.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="T33">
         <v>96.8</v>
@@ -5961,7 +5931,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>95</v>
+        <v>81.3</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -5970,7 +5940,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S34">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="T34">
         <v>96.8</v>
@@ -6038,7 +6008,7 @@
         <v>93.8</v>
       </c>
       <c r="S35">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="T35">
         <v>100</v>
@@ -6097,7 +6067,7 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -6172,7 +6142,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
@@ -6181,19 +6151,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2">
-        <v>63.6</v>
+        <v>72.7</v>
       </c>
       <c r="G2" s="2">
-        <v>36.4</v>
+        <v>27.3</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6204,7 +6174,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -6213,19 +6183,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>72.7</v>
+        <v>75.8</v>
       </c>
       <c r="G3" s="2">
-        <v>27.3</v>
+        <v>24.2</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6236,7 +6206,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -6257,7 +6227,7 @@
         <v>24.2</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6321,7 +6291,7 @@
         <v>21.2</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6455,7 +6425,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6493,16 +6463,16 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6516,10 +6486,10 @@
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -6539,16 +6509,16 @@
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6562,16 +6532,16 @@
         <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6585,16 +6555,16 @@
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6608,16 +6578,16 @@
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6631,16 +6601,16 @@
         <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6654,16 +6624,16 @@
         <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6677,10 +6647,10 @@
         <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -6700,16 +6670,16 @@
         <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6723,10 +6693,10 @@
         <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -6746,16 +6716,16 @@
         <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6769,16 +6739,16 @@
         <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6786,22 +6756,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920217</v>
+        <v>24330051920220</v>
       </c>
       <c r="B15" t="s">
         <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -6809,116 +6779,24 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920220</v>
+        <v>24330051920246</v>
       </c>
       <c r="B16" t="s">
         <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>24330051920228</v>
-      </c>
-      <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>24330051920230</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920238</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" t="s">
-        <v>97</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920246</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
     </row>
